--- a/excel_routes/route_JED_ATZ_threats.xlsx
+++ b/excel_routes/route_JED_ATZ_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801FB128-C1B4-40DE-90EE-3BA69BDA8513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5FD7D3D-6121-4E9F-B2F5-5064CFF974C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="96">
   <si>
     <t>Date</t>
   </si>
@@ -66,222 +66,231 @@
     <t>SM-456</t>
   </si>
   <si>
+    <t>EgyptAir MS-662</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>SAR</t>
+  </si>
+  <si>
+    <t>30-JUL-26</t>
+  </si>
+  <si>
+    <t>Nesma Airlines NE-171</t>
+  </si>
+  <si>
+    <t>01-AUG-26</t>
+  </si>
+  <si>
+    <t>Nesma Airlines NE-175</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-674</t>
+  </si>
+  <si>
+    <t>02-AUG-26</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-672</t>
+  </si>
+  <si>
+    <t>SM-982</t>
+  </si>
+  <si>
+    <t>Nile Air NP-128</t>
+  </si>
+  <si>
+    <t>03-AUG-26</t>
+  </si>
+  <si>
+    <t>Nesma Airlines NE-173</t>
+  </si>
+  <si>
+    <t>04-AUG-26</t>
+  </si>
+  <si>
+    <t>05-AUG-26</t>
+  </si>
+  <si>
+    <t>SM-476</t>
+  </si>
+  <si>
+    <t>flyadeal F3-777</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>Saudia SV-6897</t>
+  </si>
+  <si>
+    <t>07-AUG-26</t>
+  </si>
+  <si>
+    <t>08-AUG-26</t>
+  </si>
+  <si>
+    <t>09-AUG-26</t>
+  </si>
+  <si>
+    <t>10-AUG-26</t>
+  </si>
+  <si>
+    <t>12-AUG-26</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-670</t>
+  </si>
+  <si>
+    <t>16-AUG-26</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-666</t>
+  </si>
+  <si>
+    <t>19-AUG-26</t>
+  </si>
+  <si>
     <t>EgyptAir MS-644</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>SAR</t>
-  </si>
-  <si>
-    <t>30-JUL-26</t>
-  </si>
-  <si>
-    <t>Nesma Airlines NE-171</t>
-  </si>
-  <si>
-    <t>01-AUG-26</t>
-  </si>
-  <si>
-    <t>Nesma Airlines NE-175</t>
-  </si>
-  <si>
-    <t>02-AUG-26</t>
-  </si>
-  <si>
-    <t>flyadeal F3-777</t>
-  </si>
-  <si>
-    <t>03-AUG-26</t>
-  </si>
-  <si>
-    <t>Nesma Airlines NE-173</t>
-  </si>
-  <si>
-    <t>04-AUG-26</t>
-  </si>
-  <si>
-    <t>SM-982</t>
-  </si>
-  <si>
-    <t>05-AUG-26</t>
-  </si>
-  <si>
-    <t>07-AUG-26</t>
-  </si>
-  <si>
-    <t>08-AUG-26</t>
+    <t>22-AUG-26</t>
   </si>
   <si>
     <t>EgyptAir MS-668</t>
   </si>
   <si>
-    <t>09-AUG-26</t>
-  </si>
-  <si>
-    <t>10-AUG-26</t>
-  </si>
-  <si>
-    <t>16-AUG-26</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-666</t>
-  </si>
-  <si>
-    <t>19-AUG-26</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-662</t>
-  </si>
-  <si>
-    <t>22-AUG-26</t>
-  </si>
-  <si>
-    <t>23-AUG-26</t>
+    <t>25-AUG-26</t>
   </si>
   <si>
     <t>26-AUG-26</t>
   </si>
   <si>
-    <t>EgyptAir MS-674</t>
-  </si>
-  <si>
     <t>30-AUG-26</t>
   </si>
   <si>
-    <t>01-SEP-26</t>
+    <t>04-SEP-26</t>
+  </si>
+  <si>
+    <t>SM-986</t>
+  </si>
+  <si>
+    <t>flyadeal F3-755</t>
+  </si>
+  <si>
+    <t>13-SEP-26</t>
+  </si>
+  <si>
+    <t>flynas XY-577</t>
+  </si>
+  <si>
+    <t>15-SEP-26</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-664</t>
+  </si>
+  <si>
+    <t>18-SEP-26</t>
+  </si>
+  <si>
+    <t>Air Arabia Egypt E5-328</t>
+  </si>
+  <si>
+    <t>22-SEP-26</t>
+  </si>
+  <si>
+    <t>23-SEP-26</t>
+  </si>
+  <si>
+    <t>25-SEP-26</t>
+  </si>
+  <si>
+    <t>MED</t>
+  </si>
+  <si>
+    <t>flyadeal F3-753</t>
+  </si>
+  <si>
+    <t>26-SEP-26</t>
+  </si>
+  <si>
+    <t>27-SEP-26</t>
   </si>
   <si>
     <t>Saudia SV-307</t>
   </si>
   <si>
-    <t>04-SEP-26</t>
-  </si>
-  <si>
-    <t>SM-986</t>
+    <t>02-OCT-26</t>
+  </si>
+  <si>
+    <t>03-OCT-26</t>
+  </si>
+  <si>
+    <t>04-OCT-26</t>
+  </si>
+  <si>
+    <t>09-OCT-26</t>
+  </si>
+  <si>
+    <t>10-OCT-26</t>
+  </si>
+  <si>
+    <t>11-OCT-26</t>
+  </si>
+  <si>
+    <t>13-OCT-26</t>
+  </si>
+  <si>
+    <t>flynas XY-567</t>
+  </si>
+  <si>
+    <t>flynas XY-589</t>
+  </si>
+  <si>
+    <t>16-OCT-26</t>
+  </si>
+  <si>
+    <t>17-OCT-26</t>
+  </si>
+  <si>
+    <t>18-OCT-26</t>
+  </si>
+  <si>
+    <t>20-OCT-26</t>
   </si>
   <si>
     <t>flynas XY-565</t>
   </si>
   <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>flynas XY-583</t>
-  </si>
-  <si>
-    <t>05-SEP-26</t>
-  </si>
-  <si>
-    <t>06-SEP-26</t>
-  </si>
-  <si>
-    <t>12-SEP-26</t>
-  </si>
-  <si>
-    <t>Saudia SV-335</t>
-  </si>
-  <si>
-    <t>13-SEP-26</t>
-  </si>
-  <si>
-    <t>15-SEP-26</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-664</t>
-  </si>
-  <si>
-    <t>18-SEP-26</t>
-  </si>
-  <si>
-    <t>Nile Air NP-128</t>
-  </si>
-  <si>
-    <t>Air Arabia Egypt E5-328</t>
-  </si>
-  <si>
-    <t>22-SEP-26</t>
-  </si>
-  <si>
-    <t>23-SEP-26</t>
-  </si>
-  <si>
-    <t>25-SEP-26</t>
-  </si>
-  <si>
-    <t>flyadeal F3-755</t>
-  </si>
-  <si>
-    <t>flyadeal F3-753</t>
-  </si>
-  <si>
-    <t>MED</t>
-  </si>
-  <si>
-    <t>26-SEP-26</t>
-  </si>
-  <si>
     <t>Saudia SV-305</t>
   </si>
   <si>
-    <t>02-OCT-26</t>
-  </si>
-  <si>
-    <t>03-OCT-26</t>
-  </si>
-  <si>
-    <t>04-OCT-26</t>
-  </si>
-  <si>
-    <t>09-OCT-26</t>
-  </si>
-  <si>
-    <t>10-OCT-26</t>
-  </si>
-  <si>
-    <t>Saudia SV-301</t>
-  </si>
-  <si>
-    <t>11-OCT-26</t>
-  </si>
-  <si>
-    <t>13-OCT-26</t>
-  </si>
-  <si>
-    <t>16-OCT-26</t>
-  </si>
-  <si>
-    <t>17-OCT-26</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-670</t>
-  </si>
-  <si>
-    <t>18-OCT-26</t>
-  </si>
-  <si>
     <t>24-OCT-26</t>
   </si>
   <si>
+    <t>29-OCT-26</t>
+  </si>
+  <si>
+    <t>SM-422</t>
+  </si>
+  <si>
     <t>02-NOV-26</t>
   </si>
   <si>
-    <t>SM-422</t>
-  </si>
-  <si>
     <t>09-NOV-26</t>
   </si>
   <si>
+    <t>Air Arabia Egypt E5-362</t>
+  </si>
+  <si>
     <t>16-NOV-26</t>
   </si>
   <si>
     <t>19-NOV-26</t>
   </si>
   <si>
-    <t>EgyptAir MS-672</t>
-  </si>
-  <si>
     <t>21-NOV-26</t>
   </si>
   <si>
@@ -295,9 +304,6 @@
   </si>
   <si>
     <t>07-DEC-26</t>
-  </si>
-  <si>
-    <t>Air Arabia Egypt E5-362</t>
   </si>
   <si>
     <t>14-DEC-26</t>
@@ -712,7 +718,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K114"/>
+  <dimension ref="A1:K118"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -869,31 +875,31 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="D5" s="2">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="E5" s="2">
         <v>500</v>
       </c>
       <c r="F5" s="2">
-        <v>-101</v>
+        <v>-73</v>
       </c>
       <c r="G5" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2">
         <v>30</v>
       </c>
       <c r="I5" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>14</v>
@@ -904,31 +910,31 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D6" s="2">
-        <v>529</v>
+        <v>399</v>
       </c>
       <c r="E6" s="2">
         <v>500</v>
       </c>
       <c r="F6" s="2">
-        <v>29</v>
+        <v>-101</v>
       </c>
       <c r="G6" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H6" s="2">
         <v>30</v>
       </c>
       <c r="I6" s="2">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>14</v>
@@ -939,31 +945,31 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="D7" s="2">
-        <v>399</v>
+        <v>534</v>
       </c>
       <c r="E7" s="2">
-        <v>531</v>
+        <v>500</v>
       </c>
       <c r="F7" s="2">
-        <v>-132</v>
+        <v>34</v>
       </c>
       <c r="G7" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2">
         <v>30</v>
       </c>
       <c r="I7" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>14</v>
@@ -974,31 +980,31 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" s="2">
-        <v>399</v>
+        <v>325</v>
       </c>
       <c r="E8" s="2">
         <v>531</v>
       </c>
       <c r="F8" s="2">
-        <v>-132</v>
+        <v>-206</v>
       </c>
       <c r="G8" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2">
         <v>30</v>
       </c>
       <c r="I8" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>14</v>
@@ -1009,10 +1015,10 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>17</v>
@@ -1044,31 +1050,31 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D10" s="2">
-        <v>399</v>
+        <v>534</v>
       </c>
       <c r="E10" s="2">
         <v>531</v>
       </c>
       <c r="F10" s="2">
-        <v>-132</v>
+        <v>3</v>
       </c>
       <c r="G10" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2">
         <v>30</v>
       </c>
       <c r="I10" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>14</v>
@@ -1079,13 +1085,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D11" s="2">
         <v>399</v>
@@ -1114,13 +1120,13 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D12" s="2">
         <v>399</v>
@@ -1149,22 +1155,22 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D13" s="2">
         <v>399</v>
       </c>
       <c r="E13" s="2">
-        <v>500</v>
+        <v>531</v>
       </c>
       <c r="F13" s="2">
-        <v>-101</v>
+        <v>-132</v>
       </c>
       <c r="G13" s="2">
         <v>40</v>
@@ -1184,22 +1190,22 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D14" s="2">
         <v>399</v>
       </c>
       <c r="E14" s="2">
-        <v>500</v>
+        <v>531</v>
       </c>
       <c r="F14" s="2">
-        <v>-101</v>
+        <v>-132</v>
       </c>
       <c r="G14" s="2">
         <v>40</v>
@@ -1219,22 +1225,22 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D15" s="2">
         <v>399</v>
       </c>
       <c r="E15" s="2">
-        <v>500</v>
+        <v>531</v>
       </c>
       <c r="F15" s="2">
-        <v>-101</v>
+        <v>-132</v>
       </c>
       <c r="G15" s="2">
         <v>40</v>
@@ -1254,31 +1260,31 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D16" s="2">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="E16" s="2">
-        <v>500</v>
+        <v>531</v>
       </c>
       <c r="F16" s="2">
-        <v>-101</v>
+        <v>-104</v>
       </c>
       <c r="G16" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2">
         <v>30</v>
       </c>
       <c r="I16" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>14</v>
@@ -1289,22 +1295,22 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D17" s="2">
         <v>399</v>
       </c>
       <c r="E17" s="2">
-        <v>500</v>
+        <v>531</v>
       </c>
       <c r="F17" s="2">
-        <v>-101</v>
+        <v>-132</v>
       </c>
       <c r="G17" s="2">
         <v>40</v>
@@ -1324,22 +1330,22 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="D18" s="2">
         <v>399</v>
       </c>
       <c r="E18" s="2">
-        <v>500</v>
+        <v>531</v>
       </c>
       <c r="F18" s="2">
-        <v>-101</v>
+        <v>-132</v>
       </c>
       <c r="G18" s="2">
         <v>40</v>
@@ -1359,31 +1365,31 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D19" s="2">
-        <v>529</v>
+        <v>399</v>
       </c>
       <c r="E19" s="2">
-        <v>500</v>
+        <v>531</v>
       </c>
       <c r="F19" s="2">
-        <v>29</v>
+        <v>-132</v>
       </c>
       <c r="G19" s="2">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H19" s="2">
         <v>30</v>
       </c>
       <c r="I19" s="2">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>14</v>
@@ -1394,34 +1400,34 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D20" s="2">
-        <v>399</v>
+        <v>279</v>
       </c>
       <c r="E20" s="2">
-        <v>500</v>
+        <v>1936</v>
       </c>
       <c r="F20" s="2">
-        <v>-101</v>
+        <v>-1657</v>
       </c>
       <c r="G20" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H20" s="2">
         <v>30</v>
       </c>
       <c r="I20" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>15</v>
@@ -1432,7 +1438,7 @@
         <v>28</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>19</v>
@@ -1441,10 +1447,10 @@
         <v>399</v>
       </c>
       <c r="E21" s="2">
-        <v>468</v>
+        <v>1936</v>
       </c>
       <c r="F21" s="2">
-        <v>-69</v>
+        <v>-1537</v>
       </c>
       <c r="G21" s="2">
         <v>40</v>
@@ -1455,8 +1461,8 @@
       <c r="I21" s="2">
         <v>-10</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>14</v>
+      <c r="J21" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>15</v>
@@ -1467,31 +1473,31 @@
         <v>28</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D22" s="2">
-        <v>427</v>
+        <v>399</v>
       </c>
       <c r="E22" s="2">
-        <v>468</v>
+        <v>1936</v>
       </c>
       <c r="F22" s="2">
-        <v>-41</v>
+        <v>-1537</v>
       </c>
       <c r="G22" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H22" s="2">
         <v>30</v>
       </c>
       <c r="I22" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>14</v>
+        <v>-10</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>15</v>
@@ -1499,10 +1505,10 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>17</v>
@@ -1511,10 +1517,10 @@
         <v>399</v>
       </c>
       <c r="E23" s="2">
-        <v>468</v>
+        <v>1936</v>
       </c>
       <c r="F23" s="2">
-        <v>-69</v>
+        <v>-1537</v>
       </c>
       <c r="G23" s="2">
         <v>40</v>
@@ -1525,8 +1531,8 @@
       <c r="I23" s="2">
         <v>-10</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>14</v>
+      <c r="J23" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>15</v>
@@ -1534,34 +1540,34 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1172</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1936</v>
+      </c>
+      <c r="F24" s="2">
+        <v>-764</v>
+      </c>
+      <c r="G24" s="2">
+        <v>46</v>
+      </c>
+      <c r="H24" s="2">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2">
+        <v>-16</v>
+      </c>
+      <c r="J24" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="2">
-        <v>399</v>
-      </c>
-      <c r="E24" s="2">
-        <v>500</v>
-      </c>
-      <c r="F24" s="2">
-        <v>-101</v>
-      </c>
-      <c r="G24" s="2">
-        <v>40</v>
-      </c>
-      <c r="H24" s="2">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>15</v>
@@ -1569,13 +1575,13 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D25" s="2">
         <v>399</v>
@@ -1604,31 +1610,31 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D26" s="2">
-        <v>427</v>
+        <v>399</v>
       </c>
       <c r="E26" s="2">
         <v>468</v>
       </c>
       <c r="F26" s="2">
-        <v>-41</v>
+        <v>-69</v>
       </c>
       <c r="G26" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H26" s="2">
         <v>30</v>
       </c>
       <c r="I26" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>14</v>
@@ -1639,31 +1645,31 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D27" s="2">
-        <v>427</v>
+        <v>399</v>
       </c>
       <c r="E27" s="2">
         <v>468</v>
       </c>
       <c r="F27" s="2">
-        <v>-41</v>
+        <v>-69</v>
       </c>
       <c r="G27" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H27" s="2">
         <v>30</v>
       </c>
       <c r="I27" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>14</v>
@@ -1674,31 +1680,31 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D28" s="2">
-        <v>427</v>
+        <v>399</v>
       </c>
       <c r="E28" s="2">
         <v>500</v>
       </c>
       <c r="F28" s="2">
-        <v>-73</v>
+        <v>-101</v>
       </c>
       <c r="G28" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H28" s="2">
         <v>30</v>
       </c>
       <c r="I28" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>14</v>
@@ -1709,31 +1715,31 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D29" s="2">
-        <v>534</v>
+        <v>399</v>
       </c>
       <c r="E29" s="2">
         <v>500</v>
       </c>
       <c r="F29" s="2">
-        <v>34</v>
+        <v>-101</v>
       </c>
       <c r="G29" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H29" s="2">
         <v>30</v>
       </c>
       <c r="I29" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>14</v>
@@ -1744,13 +1750,13 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D30" s="2">
         <v>427</v>
@@ -1782,31 +1788,31 @@
         <v>37</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D31" s="2">
-        <v>529</v>
+        <v>279</v>
       </c>
       <c r="E31" s="2">
-        <v>500</v>
+        <v>1936</v>
       </c>
       <c r="F31" s="2">
-        <v>29</v>
+        <v>-1657</v>
       </c>
       <c r="G31" s="2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H31" s="2">
         <v>30</v>
       </c>
       <c r="I31" s="2">
-        <v>-2</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>15</v>
@@ -1814,34 +1820,34 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D32" s="2">
-        <v>427</v>
+        <v>399</v>
       </c>
       <c r="E32" s="2">
-        <v>468</v>
+        <v>1936</v>
       </c>
       <c r="F32" s="2">
-        <v>-41</v>
+        <v>-1537</v>
       </c>
       <c r="G32" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H32" s="2">
         <v>30</v>
       </c>
       <c r="I32" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>15</v>
@@ -1849,22 +1855,22 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D33" s="2">
         <v>427</v>
       </c>
       <c r="E33" s="2">
-        <v>500</v>
+        <v>1936</v>
       </c>
       <c r="F33" s="2">
-        <v>-73</v>
+        <v>-1509</v>
       </c>
       <c r="G33" s="2">
         <v>46</v>
@@ -1875,8 +1881,8 @@
       <c r="I33" s="2">
         <v>-16</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>14</v>
+      <c r="J33" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>15</v>
@@ -1884,22 +1890,22 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D34" s="2">
-        <v>427</v>
+        <v>534</v>
       </c>
       <c r="E34" s="2">
-        <v>500</v>
+        <v>1936</v>
       </c>
       <c r="F34" s="2">
-        <v>-73</v>
+        <v>-1402</v>
       </c>
       <c r="G34" s="2">
         <v>46</v>
@@ -1910,8 +1916,8 @@
       <c r="I34" s="2">
         <v>-16</v>
       </c>
-      <c r="J34" s="3" t="s">
-        <v>14</v>
+      <c r="J34" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>15</v>
@@ -1919,34 +1925,34 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D35" s="2">
-        <v>529</v>
+        <v>1008</v>
       </c>
       <c r="E35" s="2">
-        <v>500</v>
+        <v>1936</v>
       </c>
       <c r="F35" s="2">
-        <v>29</v>
+        <v>-928</v>
       </c>
       <c r="G35" s="2">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="H35" s="2">
         <v>30</v>
       </c>
       <c r="I35" s="2">
-        <v>-2</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>15</v>
@@ -1954,22 +1960,22 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D36" s="2">
-        <v>622</v>
+        <v>427</v>
       </c>
       <c r="E36" s="2">
-        <v>603</v>
+        <v>468</v>
       </c>
       <c r="F36" s="2">
-        <v>19</v>
+        <v>-41</v>
       </c>
       <c r="G36" s="2">
         <v>46</v>
@@ -1989,34 +1995,34 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D37" s="2">
-        <v>544</v>
+        <v>427</v>
       </c>
       <c r="E37" s="2">
-        <v>2109</v>
+        <v>500</v>
       </c>
       <c r="F37" s="2">
-        <v>-1565</v>
+        <v>-73</v>
       </c>
       <c r="G37" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H37" s="2">
         <v>30</v>
       </c>
       <c r="I37" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>46</v>
+        <v>-16</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>15</v>
@@ -2024,34 +2030,34 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D38" s="2">
-        <v>544</v>
+        <v>529</v>
       </c>
       <c r="E38" s="2">
-        <v>2109</v>
+        <v>500</v>
       </c>
       <c r="F38" s="2">
-        <v>-1565</v>
+        <v>29</v>
       </c>
       <c r="G38" s="2">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H38" s="2">
         <v>30</v>
       </c>
       <c r="I38" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>46</v>
+        <v>-2</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>15</v>
@@ -2059,22 +2065,22 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D39" s="2">
-        <v>632</v>
+        <v>534</v>
       </c>
       <c r="E39" s="2">
-        <v>2109</v>
+        <v>500</v>
       </c>
       <c r="F39" s="2">
-        <v>-1477</v>
+        <v>34</v>
       </c>
       <c r="G39" s="2">
         <v>46</v>
@@ -2085,8 +2091,8 @@
       <c r="I39" s="2">
         <v>-16</v>
       </c>
-      <c r="J39" s="4" t="s">
-        <v>46</v>
+      <c r="J39" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>15</v>
@@ -2094,22 +2100,22 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="D40" s="2">
-        <v>622</v>
+        <v>427</v>
       </c>
       <c r="E40" s="2">
-        <v>603</v>
+        <v>468</v>
       </c>
       <c r="F40" s="2">
-        <v>19</v>
+        <v>-41</v>
       </c>
       <c r="G40" s="2">
         <v>46</v>
@@ -2129,31 +2135,31 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D41" s="2">
-        <v>544</v>
+        <v>427</v>
       </c>
       <c r="E41" s="2">
-        <v>603</v>
+        <v>468</v>
       </c>
       <c r="F41" s="2">
-        <v>-59</v>
+        <v>-41</v>
       </c>
       <c r="G41" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H41" s="2">
         <v>30</v>
       </c>
       <c r="I41" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>14</v>
@@ -2164,22 +2170,22 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D42" s="2">
-        <v>622</v>
+        <v>427</v>
       </c>
       <c r="E42" s="2">
-        <v>603</v>
+        <v>468</v>
       </c>
       <c r="F42" s="2">
-        <v>19</v>
+        <v>-41</v>
       </c>
       <c r="G42" s="2">
         <v>46</v>
@@ -2199,22 +2205,22 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D43" s="2">
-        <v>622</v>
+        <v>427</v>
       </c>
       <c r="E43" s="2">
-        <v>603</v>
+        <v>500</v>
       </c>
       <c r="F43" s="2">
-        <v>19</v>
+        <v>-73</v>
       </c>
       <c r="G43" s="2">
         <v>46</v>
@@ -2234,31 +2240,31 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D44" s="2">
-        <v>544</v>
+        <v>427</v>
       </c>
       <c r="E44" s="2">
-        <v>603</v>
+        <v>500</v>
       </c>
       <c r="F44" s="2">
-        <v>-59</v>
+        <v>-73</v>
       </c>
       <c r="G44" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H44" s="2">
         <v>30</v>
       </c>
       <c r="I44" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>14</v>
@@ -2269,31 +2275,31 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="D45" s="2">
-        <v>544</v>
+        <v>427</v>
       </c>
       <c r="E45" s="2">
-        <v>603</v>
+        <v>500</v>
       </c>
       <c r="F45" s="2">
-        <v>-59</v>
+        <v>-73</v>
       </c>
       <c r="G45" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H45" s="2">
         <v>30</v>
       </c>
       <c r="I45" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>14</v>
@@ -2304,34 +2310,34 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D46" s="2">
-        <v>567</v>
+        <v>309</v>
       </c>
       <c r="E46" s="2">
-        <v>603</v>
+        <v>2109</v>
       </c>
       <c r="F46" s="2">
-        <v>-36</v>
+        <v>-1800</v>
       </c>
       <c r="G46" s="2">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H46" s="2">
         <v>30</v>
       </c>
       <c r="I46" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K46" s="2" t="s">
         <v>15</v>
@@ -2339,13 +2345,13 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="D47" s="2">
         <v>414</v>
@@ -2366,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>15</v>
@@ -2374,34 +2380,34 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D48" s="2">
-        <v>420</v>
+        <v>632</v>
       </c>
       <c r="E48" s="2">
         <v>2109</v>
       </c>
       <c r="F48" s="2">
-        <v>-1689</v>
+        <v>-1477</v>
       </c>
       <c r="G48" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H48" s="2">
         <v>30</v>
       </c>
       <c r="I48" s="2">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>15</v>
@@ -2409,34 +2415,34 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D49" s="2">
-        <v>622</v>
+        <v>534</v>
       </c>
       <c r="E49" s="2">
-        <v>2109</v>
+        <v>603</v>
       </c>
       <c r="F49" s="2">
-        <v>-1487</v>
+        <v>-69</v>
       </c>
       <c r="G49" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H49" s="2">
         <v>30</v>
       </c>
       <c r="I49" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J49" s="4" t="s">
-        <v>46</v>
+        <v>-10</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>15</v>
@@ -2444,10 +2450,10 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>54</v>
@@ -2479,34 +2485,34 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D51" s="2">
-        <v>632</v>
+        <v>369</v>
       </c>
       <c r="E51" s="2">
-        <v>603</v>
+        <v>2109</v>
       </c>
       <c r="F51" s="2">
-        <v>29</v>
+        <v>-1740</v>
       </c>
       <c r="G51" s="2">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H51" s="2">
         <v>30</v>
       </c>
       <c r="I51" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>15</v>
@@ -2514,34 +2520,34 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="D52" s="2">
-        <v>309</v>
+        <v>414</v>
       </c>
       <c r="E52" s="2">
-        <v>933</v>
+        <v>2109</v>
       </c>
       <c r="F52" s="2">
-        <v>-624</v>
+        <v>-1695</v>
       </c>
       <c r="G52" s="2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H52" s="2">
         <v>30</v>
       </c>
       <c r="I52" s="2">
-        <v>15</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>15</v>
@@ -2549,34 +2555,34 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D53" s="2">
-        <v>309</v>
+        <v>644</v>
       </c>
       <c r="E53" s="2">
-        <v>933</v>
+        <v>2109</v>
       </c>
       <c r="F53" s="2">
-        <v>-624</v>
+        <v>-1465</v>
       </c>
       <c r="G53" s="2">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H53" s="2">
         <v>30</v>
       </c>
       <c r="I53" s="2">
-        <v>15</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>14</v>
+        <v>-10</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>15</v>
@@ -2584,34 +2590,34 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D54" s="2">
-        <v>414</v>
+        <v>567</v>
       </c>
       <c r="E54" s="2">
-        <v>933</v>
+        <v>603</v>
       </c>
       <c r="F54" s="2">
-        <v>-519</v>
+        <v>-36</v>
       </c>
       <c r="G54" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H54" s="2">
         <v>30</v>
       </c>
       <c r="I54" s="2">
-        <v>0</v>
-      </c>
-      <c r="J54" s="5" t="s">
-        <v>63</v>
+        <v>-16</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>15</v>
@@ -2619,34 +2625,34 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="D55" s="2">
-        <v>414</v>
+        <v>632</v>
       </c>
       <c r="E55" s="2">
-        <v>933</v>
+        <v>603</v>
       </c>
       <c r="F55" s="2">
-        <v>-519</v>
+        <v>29</v>
       </c>
       <c r="G55" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H55" s="2">
         <v>30</v>
       </c>
       <c r="I55" s="2">
-        <v>0</v>
-      </c>
-      <c r="J55" s="5" t="s">
-        <v>63</v>
+        <v>-16</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>15</v>
@@ -2654,13 +2660,13 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D56" s="2">
         <v>479</v>
@@ -2681,7 +2687,7 @@
         <v>0</v>
       </c>
       <c r="J56" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>15</v>
@@ -2689,34 +2695,34 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D57" s="2">
-        <v>622</v>
+        <v>479</v>
       </c>
       <c r="E57" s="2">
         <v>933</v>
       </c>
       <c r="F57" s="2">
-        <v>-311</v>
+        <v>-454</v>
       </c>
       <c r="G57" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H57" s="2">
         <v>30</v>
       </c>
       <c r="I57" s="2">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K57" s="2" t="s">
         <v>15</v>
@@ -2724,34 +2730,34 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D58" s="2">
-        <v>622</v>
+        <v>644</v>
       </c>
       <c r="E58" s="2">
-        <v>603</v>
+        <v>933</v>
       </c>
       <c r="F58" s="2">
-        <v>19</v>
+        <v>-289</v>
       </c>
       <c r="G58" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H58" s="2">
         <v>30</v>
       </c>
       <c r="I58" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>14</v>
+        <v>-10</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>15</v>
@@ -2759,31 +2765,31 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D59" s="2">
-        <v>427</v>
+        <v>309</v>
       </c>
       <c r="E59" s="2">
-        <v>478</v>
+        <v>933</v>
       </c>
       <c r="F59" s="2">
-        <v>-51</v>
+        <v>-624</v>
       </c>
       <c r="G59" s="2">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H59" s="2">
         <v>30</v>
       </c>
       <c r="I59" s="2">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>14</v>
@@ -2794,31 +2800,31 @@
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="D60" s="2">
-        <v>534</v>
+        <v>309</v>
       </c>
       <c r="E60" s="2">
-        <v>603</v>
+        <v>933</v>
       </c>
       <c r="F60" s="2">
-        <v>-69</v>
+        <v>-624</v>
       </c>
       <c r="G60" s="2">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H60" s="2">
         <v>30</v>
       </c>
       <c r="I60" s="2">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>14</v>
@@ -2829,34 +2835,34 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D61" s="2">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="E61" s="2">
-        <v>478</v>
+        <v>933</v>
       </c>
       <c r="F61" s="2">
-        <v>-51</v>
+        <v>-519</v>
       </c>
       <c r="G61" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H61" s="2">
         <v>30</v>
       </c>
       <c r="I61" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>15</v>
@@ -2864,22 +2870,22 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="D62" s="2">
-        <v>427</v>
+        <v>622</v>
       </c>
       <c r="E62" s="2">
         <v>603</v>
       </c>
       <c r="F62" s="2">
-        <v>-176</v>
+        <v>19</v>
       </c>
       <c r="G62" s="2">
         <v>46</v>
@@ -2890,8 +2896,8 @@
       <c r="I62" s="2">
         <v>-16</v>
       </c>
-      <c r="J62" s="5" t="s">
-        <v>63</v>
+      <c r="J62" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>15</v>
@@ -2899,13 +2905,13 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D63" s="2">
         <v>427</v>
@@ -2934,13 +2940,13 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="D64" s="2">
         <v>534</v>
@@ -2969,22 +2975,22 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="D65" s="2">
-        <v>622</v>
+        <v>427</v>
       </c>
       <c r="E65" s="2">
-        <v>603</v>
+        <v>478</v>
       </c>
       <c r="F65" s="2">
-        <v>19</v>
+        <v>-51</v>
       </c>
       <c r="G65" s="2">
         <v>46</v>
@@ -3004,22 +3010,22 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D66" s="2">
-        <v>534</v>
+        <v>427</v>
       </c>
       <c r="E66" s="2">
         <v>603</v>
       </c>
       <c r="F66" s="2">
-        <v>-69</v>
+        <v>-176</v>
       </c>
       <c r="G66" s="2">
         <v>46</v>
@@ -3030,8 +3036,8 @@
       <c r="I66" s="2">
         <v>-16</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>14</v>
+      <c r="J66" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>15</v>
@@ -3039,22 +3045,22 @@
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D67" s="2">
-        <v>534</v>
+        <v>427</v>
       </c>
       <c r="E67" s="2">
-        <v>603</v>
+        <v>478</v>
       </c>
       <c r="F67" s="2">
-        <v>-69</v>
+        <v>-51</v>
       </c>
       <c r="G67" s="2">
         <v>46</v>
@@ -3074,22 +3080,22 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D68" s="2">
-        <v>427</v>
+        <v>534</v>
       </c>
       <c r="E68" s="2">
-        <v>478</v>
+        <v>603</v>
       </c>
       <c r="F68" s="2">
-        <v>-51</v>
+        <v>-69</v>
       </c>
       <c r="G68" s="2">
         <v>46</v>
@@ -3109,22 +3115,22 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="D69" s="2">
-        <v>427</v>
+        <v>534</v>
       </c>
       <c r="E69" s="2">
-        <v>478</v>
+        <v>603</v>
       </c>
       <c r="F69" s="2">
-        <v>-51</v>
+        <v>-69</v>
       </c>
       <c r="G69" s="2">
         <v>46</v>
@@ -3144,34 +3150,34 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D70" s="2">
-        <v>427</v>
+        <v>534</v>
       </c>
       <c r="E70" s="2">
         <v>603</v>
       </c>
       <c r="F70" s="2">
-        <v>-176</v>
+        <v>-69</v>
       </c>
       <c r="G70" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H70" s="2">
         <v>30</v>
       </c>
       <c r="I70" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J70" s="5" t="s">
-        <v>63</v>
+        <v>-10</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>15</v>
@@ -3179,31 +3185,31 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="D71" s="2">
-        <v>427</v>
+        <v>534</v>
       </c>
       <c r="E71" s="2">
-        <v>478</v>
+        <v>603</v>
       </c>
       <c r="F71" s="2">
-        <v>-51</v>
+        <v>-69</v>
       </c>
       <c r="G71" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H71" s="2">
         <v>30</v>
       </c>
       <c r="I71" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J71" s="3" t="s">
         <v>14</v>
@@ -3214,31 +3220,31 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D72" s="2">
-        <v>427</v>
+        <v>534</v>
       </c>
       <c r="E72" s="2">
-        <v>478</v>
+        <v>603</v>
       </c>
       <c r="F72" s="2">
-        <v>-51</v>
+        <v>-69</v>
       </c>
       <c r="G72" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H72" s="2">
         <v>30</v>
       </c>
       <c r="I72" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>14</v>
@@ -3249,22 +3255,22 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D73" s="2">
         <v>427</v>
       </c>
       <c r="E73" s="2">
-        <v>603</v>
+        <v>478</v>
       </c>
       <c r="F73" s="2">
-        <v>-176</v>
+        <v>-51</v>
       </c>
       <c r="G73" s="2">
         <v>46</v>
@@ -3275,8 +3281,8 @@
       <c r="I73" s="2">
         <v>-16</v>
       </c>
-      <c r="J73" s="5" t="s">
-        <v>63</v>
+      <c r="J73" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>15</v>
@@ -3284,22 +3290,22 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D74" s="2">
-        <v>427</v>
+        <v>534</v>
       </c>
       <c r="E74" s="2">
         <v>603</v>
       </c>
       <c r="F74" s="2">
-        <v>-176</v>
+        <v>-69</v>
       </c>
       <c r="G74" s="2">
         <v>46</v>
@@ -3310,8 +3316,8 @@
       <c r="I74" s="2">
         <v>-16</v>
       </c>
-      <c r="J74" s="5" t="s">
-        <v>63</v>
+      <c r="J74" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>15</v>
@@ -3319,22 +3325,22 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D75" s="2">
-        <v>622</v>
+        <v>427</v>
       </c>
       <c r="E75" s="2">
-        <v>603</v>
+        <v>478</v>
       </c>
       <c r="F75" s="2">
-        <v>19</v>
+        <v>-51</v>
       </c>
       <c r="G75" s="2">
         <v>46</v>
@@ -3354,13 +3360,13 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D76" s="2">
         <v>427</v>
@@ -3389,13 +3395,13 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D77" s="2">
         <v>427</v>
@@ -3416,7 +3422,7 @@
         <v>-16</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>15</v>
@@ -3424,22 +3430,22 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D78" s="2">
-        <v>567</v>
+        <v>427</v>
       </c>
       <c r="E78" s="2">
         <v>603</v>
       </c>
       <c r="F78" s="2">
-        <v>-36</v>
+        <v>-176</v>
       </c>
       <c r="G78" s="2">
         <v>46</v>
@@ -3450,8 +3456,8 @@
       <c r="I78" s="2">
         <v>-16</v>
       </c>
-      <c r="J78" s="3" t="s">
-        <v>14</v>
+      <c r="J78" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="K78" s="2" t="s">
         <v>15</v>
@@ -3459,31 +3465,31 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="D79" s="2">
-        <v>622</v>
+        <v>534</v>
       </c>
       <c r="E79" s="2">
         <v>603</v>
       </c>
       <c r="F79" s="2">
-        <v>19</v>
+        <v>-69</v>
       </c>
       <c r="G79" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H79" s="2">
         <v>30</v>
       </c>
       <c r="I79" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J79" s="3" t="s">
         <v>14</v>
@@ -3494,31 +3500,31 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="D80" s="2">
-        <v>415</v>
+        <v>622</v>
       </c>
       <c r="E80" s="2">
-        <v>783</v>
+        <v>603</v>
       </c>
       <c r="F80" s="2">
-        <v>-368</v>
+        <v>19</v>
       </c>
       <c r="G80" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H80" s="2">
         <v>30</v>
       </c>
       <c r="I80" s="2">
-        <v>10</v>
+        <v>-16</v>
       </c>
       <c r="J80" s="3" t="s">
         <v>14</v>
@@ -3529,31 +3535,31 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D81" s="2">
-        <v>549</v>
+        <v>427</v>
       </c>
       <c r="E81" s="2">
-        <v>783</v>
+        <v>478</v>
       </c>
       <c r="F81" s="2">
-        <v>-234</v>
+        <v>-51</v>
       </c>
       <c r="G81" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H81" s="2">
         <v>30</v>
       </c>
       <c r="I81" s="2">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>14</v>
@@ -3564,22 +3570,22 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D82" s="2">
-        <v>619</v>
+        <v>427</v>
       </c>
       <c r="E82" s="2">
-        <v>783</v>
+        <v>603</v>
       </c>
       <c r="F82" s="2">
-        <v>-164</v>
+        <v>-176</v>
       </c>
       <c r="G82" s="2">
         <v>46</v>
@@ -3591,7 +3597,7 @@
         <v>-16</v>
       </c>
       <c r="J82" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>15</v>
@@ -3599,31 +3605,31 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="D83" s="2">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="E83" s="2">
-        <v>783</v>
+        <v>603</v>
       </c>
       <c r="F83" s="2">
-        <v>-234</v>
+        <v>-36</v>
       </c>
       <c r="G83" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H83" s="2">
         <v>30</v>
       </c>
       <c r="I83" s="2">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>14</v>
@@ -3637,19 +3643,19 @@
         <v>81</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="D84" s="2">
-        <v>622</v>
+        <v>427</v>
       </c>
       <c r="E84" s="2">
-        <v>783</v>
+        <v>478</v>
       </c>
       <c r="F84" s="2">
-        <v>-161</v>
+        <v>-51</v>
       </c>
       <c r="G84" s="2">
         <v>46</v>
@@ -3660,8 +3666,8 @@
       <c r="I84" s="2">
         <v>-16</v>
       </c>
-      <c r="J84" s="5" t="s">
-        <v>63</v>
+      <c r="J84" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K84" s="2" t="s">
         <v>15</v>
@@ -3669,31 +3675,31 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="D85" s="2">
-        <v>719</v>
+        <v>413</v>
       </c>
       <c r="E85" s="2">
         <v>783</v>
       </c>
       <c r="F85" s="2">
-        <v>-64</v>
+        <v>-370</v>
       </c>
       <c r="G85" s="2">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H85" s="2">
         <v>30</v>
       </c>
       <c r="I85" s="2">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="J85" s="3" t="s">
         <v>14</v>
@@ -3704,31 +3710,31 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="C86" s="2" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="D86" s="2">
-        <v>415</v>
+        <v>549</v>
       </c>
       <c r="E86" s="2">
         <v>783</v>
       </c>
       <c r="F86" s="2">
-        <v>-368</v>
+        <v>-234</v>
       </c>
       <c r="G86" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H86" s="2">
         <v>30</v>
       </c>
       <c r="I86" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J86" s="3" t="s">
         <v>14</v>
@@ -3739,34 +3745,34 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="C87" s="2" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="D87" s="2">
-        <v>549</v>
+        <v>619</v>
       </c>
       <c r="E87" s="2">
         <v>783</v>
       </c>
       <c r="F87" s="2">
-        <v>-234</v>
+        <v>-164</v>
       </c>
       <c r="G87" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H87" s="2">
         <v>30</v>
       </c>
       <c r="I87" s="2">
-        <v>0</v>
-      </c>
-      <c r="J87" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J87" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>15</v>
@@ -3774,34 +3780,34 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="C88" s="2" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="D88" s="2">
-        <v>622</v>
+        <v>549</v>
       </c>
       <c r="E88" s="2">
         <v>783</v>
       </c>
       <c r="F88" s="2">
-        <v>-161</v>
+        <v>-234</v>
       </c>
       <c r="G88" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H88" s="2">
         <v>30</v>
       </c>
       <c r="I88" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J88" s="5" t="s">
-        <v>63</v>
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>15</v>
@@ -3809,34 +3815,34 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="D89" s="2">
-        <v>534</v>
+        <v>638</v>
       </c>
       <c r="E89" s="2">
         <v>783</v>
       </c>
       <c r="F89" s="2">
-        <v>-249</v>
+        <v>-145</v>
       </c>
       <c r="G89" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H89" s="2">
         <v>30</v>
       </c>
       <c r="I89" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J89" s="5" t="s">
-        <v>63</v>
+        <v>-10</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>15</v>
@@ -3844,22 +3850,22 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="D90" s="2">
-        <v>569</v>
+        <v>719</v>
       </c>
       <c r="E90" s="2">
         <v>783</v>
       </c>
       <c r="F90" s="2">
-        <v>-214</v>
+        <v>-64</v>
       </c>
       <c r="G90" s="2">
         <v>46</v>
@@ -3870,8 +3876,8 @@
       <c r="I90" s="2">
         <v>-16</v>
       </c>
-      <c r="J90" s="5" t="s">
-        <v>63</v>
+      <c r="J90" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K90" s="2" t="s">
         <v>15</v>
@@ -3879,34 +3885,34 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="D91" s="2">
-        <v>619</v>
+        <v>413</v>
       </c>
       <c r="E91" s="2">
         <v>783</v>
       </c>
       <c r="F91" s="2">
-        <v>-164</v>
+        <v>-370</v>
       </c>
       <c r="G91" s="2">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H91" s="2">
         <v>30</v>
       </c>
       <c r="I91" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J91" s="5" t="s">
-        <v>63</v>
+        <v>10</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K91" s="2" t="s">
         <v>15</v>
@@ -3914,34 +3920,34 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="D92" s="2">
-        <v>534</v>
+        <v>413</v>
       </c>
       <c r="E92" s="2">
         <v>783</v>
       </c>
       <c r="F92" s="2">
-        <v>-249</v>
+        <v>-370</v>
       </c>
       <c r="G92" s="2">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H92" s="2">
         <v>30</v>
       </c>
       <c r="I92" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J92" s="5" t="s">
-        <v>63</v>
+        <v>10</v>
+      </c>
+      <c r="J92" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K92" s="2" t="s">
         <v>15</v>
@@ -3949,34 +3955,34 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D93" s="2">
-        <v>619</v>
+        <v>549</v>
       </c>
       <c r="E93" s="2">
         <v>783</v>
       </c>
       <c r="F93" s="2">
-        <v>-164</v>
+        <v>-234</v>
       </c>
       <c r="G93" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H93" s="2">
         <v>30</v>
       </c>
       <c r="I93" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J93" s="5" t="s">
-        <v>63</v>
+        <v>0</v>
+      </c>
+      <c r="J93" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K93" s="2" t="s">
         <v>15</v>
@@ -3984,22 +3990,22 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D94" s="2">
-        <v>719</v>
+        <v>534</v>
       </c>
       <c r="E94" s="2">
         <v>783</v>
       </c>
       <c r="F94" s="2">
-        <v>-64</v>
+        <v>-249</v>
       </c>
       <c r="G94" s="2">
         <v>46</v>
@@ -4010,8 +4016,8 @@
       <c r="I94" s="2">
         <v>-16</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>14</v>
+      <c r="J94" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="K94" s="2" t="s">
         <v>15</v>
@@ -4019,34 +4025,34 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="D95" s="2">
-        <v>549</v>
+        <v>569</v>
       </c>
       <c r="E95" s="2">
         <v>783</v>
       </c>
       <c r="F95" s="2">
-        <v>-234</v>
+        <v>-214</v>
       </c>
       <c r="G95" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H95" s="2">
         <v>30</v>
       </c>
       <c r="I95" s="2">
-        <v>0</v>
-      </c>
-      <c r="J95" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J95" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="K95" s="2" t="s">
         <v>15</v>
@@ -4054,13 +4060,13 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D96" s="2">
         <v>619</v>
@@ -4081,7 +4087,7 @@
         <v>-16</v>
       </c>
       <c r="J96" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K96" s="2" t="s">
         <v>15</v>
@@ -4089,34 +4095,34 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="D97" s="2">
-        <v>549</v>
+        <v>534</v>
       </c>
       <c r="E97" s="2">
         <v>783</v>
       </c>
       <c r="F97" s="2">
-        <v>-234</v>
+        <v>-249</v>
       </c>
       <c r="G97" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H97" s="2">
         <v>30</v>
       </c>
       <c r="I97" s="2">
-        <v>0</v>
-      </c>
-      <c r="J97" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J97" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="K97" s="2" t="s">
         <v>15</v>
@@ -4124,22 +4130,22 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D98" s="2">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="E98" s="2">
         <v>783</v>
       </c>
       <c r="F98" s="2">
-        <v>-161</v>
+        <v>-164</v>
       </c>
       <c r="G98" s="2">
         <v>46</v>
@@ -4151,7 +4157,7 @@
         <v>-16</v>
       </c>
       <c r="J98" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K98" s="2" t="s">
         <v>15</v>
@@ -4159,31 +4165,31 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="D99" s="2">
-        <v>641</v>
+        <v>719</v>
       </c>
       <c r="E99" s="2">
         <v>783</v>
       </c>
       <c r="F99" s="2">
-        <v>-142</v>
+        <v>-64</v>
       </c>
       <c r="G99" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H99" s="2">
         <v>30</v>
       </c>
       <c r="I99" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J99" s="3" t="s">
         <v>14</v>
@@ -4194,34 +4200,34 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D100" s="2">
-        <v>534</v>
+        <v>549</v>
       </c>
       <c r="E100" s="2">
         <v>783</v>
       </c>
       <c r="F100" s="2">
-        <v>-249</v>
+        <v>-234</v>
       </c>
       <c r="G100" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H100" s="2">
         <v>30</v>
       </c>
       <c r="I100" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J100" s="5" t="s">
-        <v>63</v>
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K100" s="2" t="s">
         <v>15</v>
@@ -4229,22 +4235,22 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="D101" s="2">
-        <v>569</v>
+        <v>619</v>
       </c>
       <c r="E101" s="2">
         <v>783</v>
       </c>
       <c r="F101" s="2">
-        <v>-214</v>
+        <v>-164</v>
       </c>
       <c r="G101" s="2">
         <v>46</v>
@@ -4256,7 +4262,7 @@
         <v>-16</v>
       </c>
       <c r="J101" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K101" s="2" t="s">
         <v>15</v>
@@ -4264,34 +4270,34 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D102" s="2">
-        <v>622</v>
+        <v>413</v>
       </c>
       <c r="E102" s="2">
         <v>783</v>
       </c>
       <c r="F102" s="2">
-        <v>-161</v>
+        <v>-370</v>
       </c>
       <c r="G102" s="2">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H102" s="2">
         <v>30</v>
       </c>
       <c r="I102" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J102" s="5" t="s">
-        <v>63</v>
+        <v>10</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K102" s="2" t="s">
         <v>15</v>
@@ -4299,22 +4305,22 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D103" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E103" s="2">
         <v>783</v>
       </c>
       <c r="F103" s="2">
-        <v>-369</v>
+        <v>-370</v>
       </c>
       <c r="G103" s="2">
         <v>20</v>
@@ -4334,13 +4340,13 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="D104" s="2">
         <v>549</v>
@@ -4369,34 +4375,34 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="D105" s="2">
-        <v>641</v>
+        <v>534</v>
       </c>
       <c r="E105" s="2">
         <v>783</v>
       </c>
       <c r="F105" s="2">
-        <v>-142</v>
+        <v>-249</v>
       </c>
       <c r="G105" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H105" s="2">
         <v>30</v>
       </c>
       <c r="I105" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J105" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J105" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="K105" s="2" t="s">
         <v>15</v>
@@ -4407,28 +4413,28 @@
         <v>91</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="D106" s="2">
-        <v>414</v>
+        <v>549</v>
       </c>
       <c r="E106" s="2">
         <v>783</v>
       </c>
       <c r="F106" s="2">
-        <v>-369</v>
+        <v>-234</v>
       </c>
       <c r="G106" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H106" s="2">
         <v>30</v>
       </c>
       <c r="I106" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J106" s="3" t="s">
         <v>14</v>
@@ -4442,31 +4448,31 @@
         <v>91</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="D107" s="2">
-        <v>414</v>
+        <v>569</v>
       </c>
       <c r="E107" s="2">
         <v>783</v>
       </c>
       <c r="F107" s="2">
-        <v>-369</v>
+        <v>-214</v>
       </c>
       <c r="G107" s="2">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="H107" s="2">
         <v>30</v>
       </c>
       <c r="I107" s="2">
-        <v>10</v>
-      </c>
-      <c r="J107" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J107" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="K107" s="2" t="s">
         <v>15</v>
@@ -4474,31 +4480,31 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D108" s="2">
-        <v>549</v>
+        <v>413</v>
       </c>
       <c r="E108" s="2">
         <v>783</v>
       </c>
       <c r="F108" s="2">
-        <v>-234</v>
+        <v>-370</v>
       </c>
       <c r="G108" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H108" s="2">
         <v>30</v>
       </c>
       <c r="I108" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J108" s="3" t="s">
         <v>14</v>
@@ -4512,19 +4518,19 @@
         <v>92</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D109" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E109" s="2">
         <v>783</v>
       </c>
       <c r="F109" s="2">
-        <v>-369</v>
+        <v>-370</v>
       </c>
       <c r="G109" s="2">
         <v>20</v>
@@ -4547,28 +4553,28 @@
         <v>92</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="D110" s="2">
-        <v>414</v>
+        <v>549</v>
       </c>
       <c r="E110" s="2">
         <v>783</v>
       </c>
       <c r="F110" s="2">
-        <v>-369</v>
+        <v>-234</v>
       </c>
       <c r="G110" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H110" s="2">
         <v>30</v>
       </c>
       <c r="I110" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J110" s="3" t="s">
         <v>14</v>
@@ -4579,31 +4585,31 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D111" s="2">
-        <v>549</v>
+        <v>413</v>
       </c>
       <c r="E111" s="2">
         <v>783</v>
       </c>
       <c r="F111" s="2">
-        <v>-234</v>
+        <v>-370</v>
       </c>
       <c r="G111" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H111" s="2">
         <v>30</v>
       </c>
       <c r="I111" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J111" s="3" t="s">
         <v>14</v>
@@ -4617,19 +4623,19 @@
         <v>93</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D112" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E112" s="2">
         <v>783</v>
       </c>
       <c r="F112" s="2">
-        <v>-369</v>
+        <v>-370</v>
       </c>
       <c r="G112" s="2">
         <v>20</v>
@@ -4652,28 +4658,28 @@
         <v>93</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="D113" s="2">
-        <v>414</v>
+        <v>549</v>
       </c>
       <c r="E113" s="2">
         <v>783</v>
       </c>
       <c r="F113" s="2">
-        <v>-369</v>
+        <v>-234</v>
       </c>
       <c r="G113" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H113" s="2">
         <v>30</v>
       </c>
       <c r="I113" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J113" s="3" t="s">
         <v>14</v>
@@ -4684,36 +4690,176 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D114" s="2">
-        <v>622</v>
+        <v>413</v>
       </c>
       <c r="E114" s="2">
         <v>783</v>
       </c>
       <c r="F114" s="2">
-        <v>-161</v>
+        <v>-370</v>
       </c>
       <c r="G114" s="2">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="H114" s="2">
         <v>30</v>
       </c>
       <c r="I114" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J114" s="5" t="s">
-        <v>63</v>
+        <v>10</v>
+      </c>
+      <c r="J114" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K114" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D115" s="2">
+        <v>413</v>
+      </c>
+      <c r="E115" s="2">
+        <v>783</v>
+      </c>
+      <c r="F115" s="2">
+        <v>-370</v>
+      </c>
+      <c r="G115" s="2">
+        <v>20</v>
+      </c>
+      <c r="H115" s="2">
+        <v>30</v>
+      </c>
+      <c r="I115" s="2">
+        <v>10</v>
+      </c>
+      <c r="J115" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D116" s="2">
+        <v>549</v>
+      </c>
+      <c r="E116" s="2">
+        <v>783</v>
+      </c>
+      <c r="F116" s="2">
+        <v>-234</v>
+      </c>
+      <c r="G116" s="2">
+        <v>30</v>
+      </c>
+      <c r="H116" s="2">
+        <v>30</v>
+      </c>
+      <c r="I116" s="2">
+        <v>0</v>
+      </c>
+      <c r="J116" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K116" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D117" s="2">
+        <v>413</v>
+      </c>
+      <c r="E117" s="2">
+        <v>783</v>
+      </c>
+      <c r="F117" s="2">
+        <v>-370</v>
+      </c>
+      <c r="G117" s="2">
+        <v>20</v>
+      </c>
+      <c r="H117" s="2">
+        <v>30</v>
+      </c>
+      <c r="I117" s="2">
+        <v>10</v>
+      </c>
+      <c r="J117" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K117" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D118" s="2">
+        <v>413</v>
+      </c>
+      <c r="E118" s="2">
+        <v>783</v>
+      </c>
+      <c r="F118" s="2">
+        <v>-370</v>
+      </c>
+      <c r="G118" s="2">
+        <v>20</v>
+      </c>
+      <c r="H118" s="2">
+        <v>30</v>
+      </c>
+      <c r="I118" s="2">
+        <v>10</v>
+      </c>
+      <c r="J118" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K118" s="2" t="s">
         <v>15</v>
       </c>
     </row>
